--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -53,12 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
   </si>
   <si>
     <t>В4450ТТ</t>
@@ -113,8 +107,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -200,11 +195,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -212,9 +208,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,20 +564,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46146</v>
       </c>
       <c r="B2">
         <v>1199</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
       </c>
       <c r="F2">
         <v>61.539</v>
@@ -599,7 +595,7 @@
         <v>110.77</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -609,20 +605,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46149</v>
       </c>
       <c r="B3">
         <v>1199</v>
       </c>
       <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>74.361</v>
@@ -640,7 +636,7 @@
         <v>133.85</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -650,80 +646,80 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6">
         <v>135.9</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>2</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="6">
         <v>1.77</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="6">
         <v>240.54</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="6">
         <v>244.62</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <v>4.08</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="7">
+      <c r="A9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="8">
         <v>135.9</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>2</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8">
         <v>240.54</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>244.62</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <v>4.08</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -143,7 +143,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,12 +153,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -209,17 +203,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,16 +46,16 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В4450ТТ</t>
@@ -74,21 +71,6 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:55:00</t>
-  </si>
-  <si>
-    <t>09:54:00</t>
-  </si>
-  <si>
-    <t>3232159322 3232159322</t>
-  </si>
-  <si>
-    <t>3232208575 3232208575</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДМ</t>
@@ -508,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -517,17 +499,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -561,175 +540,183 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>53.19</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H2">
+        <v>88.3</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J2">
+        <v>89.89</v>
+      </c>
+      <c r="K2">
+        <v>46055</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>71.42</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="H3">
+        <v>116.41</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="J3">
+        <v>118.56</v>
+      </c>
+      <c r="K3">
+        <v>184162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>62.3</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H4">
+        <v>99.06</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="J4">
+        <v>100.93</v>
+      </c>
+      <c r="K4">
+        <v>46564</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>62.17</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>1.72</v>
-      </c>
-      <c r="I2" s="1">
-        <v>106.93</v>
-      </c>
-      <c r="J2">
-        <v>1.75</v>
-      </c>
-      <c r="K2" s="1">
-        <v>108.8</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M2">
-        <v>45528</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="C8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46164</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>75.15000000000001</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3">
-        <v>1.72</v>
-      </c>
-      <c r="I3" s="1">
-        <v>129.26</v>
-      </c>
-      <c r="J3">
-        <v>1.75</v>
-      </c>
-      <c r="K3" s="1">
-        <v>131.51</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
-        <v>183394</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="B9" s="7">
+        <v>186.91</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.6252</v>
+      </c>
+      <c r="E9" s="7">
+        <v>303.77</v>
+      </c>
+      <c r="F9" s="7">
+        <v>309.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="7">
-        <v>137.32</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1.72</v>
-      </c>
-      <c r="E8" s="7">
-        <v>236.19</v>
-      </c>
-      <c r="F8" s="7">
-        <v>240.31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="10">
-        <v>137.32</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>236.19</v>
-      </c>
-      <c r="F9" s="10">
-        <v>240.31</v>
+      <c r="B10" s="10">
+        <v>186.91</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>303.77</v>
+      </c>
+      <c r="F10" s="10">
+        <v>309.38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -46,13 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>Варна Чайка</t>
@@ -71,6 +77,15 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>16:56</t>
+  </si>
+  <si>
+    <t>14:04</t>
+  </si>
+  <si>
+    <t>12:08</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДМ</t>
@@ -490,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -503,10 +518,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -540,22 +557,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46175</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>53.19</v>
@@ -572,25 +595,31 @@
       <c r="J2">
         <v>89.89</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2">
         <v>46055</v>
       </c>
+      <c r="M2">
+        <v>191727</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46178</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>71.42</v>
@@ -607,25 +636,31 @@
       <c r="J3">
         <v>118.56</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
         <v>184162</v>
       </c>
+      <c r="M3">
+        <v>272770</v>
+      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46184</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>62.3</v>
@@ -642,13 +677,19 @@
       <c r="J4">
         <v>100.93</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4">
         <v>46564</v>
       </c>
+      <c r="M4">
+        <v>111276</v>
+      </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -656,18 +697,18 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>7</v>
@@ -676,9 +717,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7">
         <v>186.91</v>
@@ -696,9 +737,9 @@
         <v>309.38</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B10" s="10">
         <v>186.91</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -49,21 +49,12 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
     <t>В4450ТТ</t>
   </si>
   <si>
@@ -79,13 +70,10 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>16:56</t>
-  </si>
-  <si>
-    <t>14:04</t>
-  </si>
-  <si>
-    <t>12:08</t>
+    <t>2026-06-22 09:19:10</t>
+  </si>
+  <si>
+    <t>2026-06-22 11:06:18</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДМ</t>
@@ -505,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,12 +506,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -557,207 +543,148 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>54.72</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H2">
+        <v>81.53</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J2">
+        <v>83.17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H3">
+        <v>113.02</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J3">
+        <v>115.29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46175</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>53.19</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="H2">
-        <v>88.3</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J2">
-        <v>89.89</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L2">
-        <v>46055</v>
-      </c>
-      <c r="M2">
-        <v>191727</v>
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46178</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>71.42</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="H3">
-        <v>116.41</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="J3">
-        <v>118.56</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>184162</v>
-      </c>
-      <c r="M3">
-        <v>272770</v>
+      <c r="B8" s="7">
+        <v>130.57</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1.49</v>
+      </c>
+      <c r="E8" s="7">
+        <v>194.55</v>
+      </c>
+      <c r="F8" s="7">
+        <v>198.46</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>62.3</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="H4">
-        <v>99.06</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="J4">
-        <v>100.93</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4">
-        <v>46564</v>
-      </c>
-      <c r="M4">
-        <v>111276</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="7">
-        <v>186.91</v>
-      </c>
-      <c r="C9" s="7">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.6252</v>
-      </c>
-      <c r="E9" s="7">
-        <v>303.77</v>
-      </c>
-      <c r="F9" s="7">
-        <v>309.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="10">
-        <v>186.91</v>
-      </c>
-      <c r="C10" s="10">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>303.77</v>
-      </c>
-      <c r="F10" s="10">
-        <v>309.38</v>
+      <c r="B9" s="10">
+        <v>130.57</v>
+      </c>
+      <c r="C9" s="10">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="10">
+        <v>194.55</v>
+      </c>
+      <c r="F9" s="10">
+        <v>198.46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,10 +52,16 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>В4450ТТ</t>
@@ -70,10 +79,25 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-22 09:19:10</t>
-  </si>
-  <si>
-    <t>2026-06-22 11:06:18</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:19:00</t>
+  </si>
+  <si>
+    <t>11:06:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>3233710338 3233710338</t>
+  </si>
+  <si>
+    <t>3233716704 3233716704</t>
+  </si>
+  <si>
+    <t>3234050523 3234050523</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДМ</t>
@@ -493,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -502,14 +526,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,148 +570,219 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46195</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>54.72</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
         <v>1.49</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>81.53</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>83.17</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>47040</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46195</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>75.84999999999999</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
         <v>1.49</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>113.02</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>115.29</v>
       </c>
-      <c r="K3" t="s">
-        <v>19</v>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>184900</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="4" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="F4">
+        <v>58.86</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4">
+        <v>1.48</v>
+      </c>
+      <c r="I4" s="1">
+        <v>87.11</v>
+      </c>
+      <c r="J4">
+        <v>1.51</v>
+      </c>
+      <c r="K4" s="1">
+        <v>88.88</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>47503</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="7">
-        <v>130.57</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1.49</v>
-      </c>
-      <c r="E8" s="7">
-        <v>194.55</v>
-      </c>
-      <c r="F8" s="7">
-        <v>198.46</v>
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="10">
-        <v>130.57</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>194.55</v>
-      </c>
-      <c r="F9" s="10">
-        <v>198.46</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="7">
+        <v>189.43</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.4869</v>
+      </c>
+      <c r="E9" s="7">
+        <v>281.66</v>
+      </c>
+      <c r="F9" s="7">
+        <v>287.34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="10">
+        <v>189.43</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>281.66</v>
+      </c>
+      <c r="F10" s="10">
+        <v>287.34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
   </si>
   <si>
     <t>В4450ТТ</t>
@@ -79,25 +76,13 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:19:00</t>
-  </si>
-  <si>
-    <t>11:06:00</t>
-  </si>
-  <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>3233710338 3233710338</t>
-  </si>
-  <si>
-    <t>3233716704 3233716704</t>
-  </si>
-  <si>
-    <t>3234050523 3234050523</t>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>13:00</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДМ</t>
@@ -517,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -526,17 +511,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -576,145 +560,133 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46195</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>54.72</v>
       </c>
-      <c r="G2" t="s">
-        <v>21</v>
+      <c r="G2" s="1">
+        <v>1.49</v>
       </c>
       <c r="H2">
-        <v>1.49</v>
+        <v>81.53</v>
       </c>
       <c r="I2" s="1">
-        <v>81.53</v>
+        <v>1.52</v>
       </c>
       <c r="J2">
-        <v>1.52</v>
-      </c>
-      <c r="K2" s="1">
         <v>83.17</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>246997</v>
       </c>
       <c r="M2">
-        <v>47040</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
+        <v>144445</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46195</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
       </c>
       <c r="F3">
         <v>75.84999999999999</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H3">
+        <v>113.02</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J3">
+        <v>115.29</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="H3">
-        <v>1.49</v>
-      </c>
-      <c r="I3" s="1">
-        <v>113.02</v>
-      </c>
-      <c r="J3">
-        <v>1.52</v>
-      </c>
-      <c r="K3" s="1">
-        <v>115.29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
+      <c r="L3">
+        <v>184900</v>
       </c>
       <c r="M3">
-        <v>184900</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
+        <v>203408</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46202</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>58.86</v>
       </c>
-      <c r="G4" t="s">
-        <v>21</v>
+      <c r="G4" s="1">
+        <v>1.48</v>
       </c>
       <c r="H4">
-        <v>1.48</v>
+        <v>87.11</v>
       </c>
       <c r="I4" s="1">
-        <v>87.11</v>
+        <v>1.51</v>
       </c>
       <c r="J4">
-        <v>1.51</v>
-      </c>
-      <c r="K4" s="1">
         <v>88.88</v>
       </c>
-      <c r="L4" t="s">
-        <v>24</v>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4">
+        <v>47503</v>
       </c>
       <c r="M4">
-        <v>47503</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
+        <v>120389</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -722,29 +694,29 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7">
         <v>189.43</v>
@@ -762,9 +734,9 @@
         <v>287.34</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B10" s="10">
         <v>189.43</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,25 +55,28 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>В4450ТТ</t>
-  </si>
-  <si>
-    <t>78970155027721160</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>В3270ВН</t>
+  </si>
+  <si>
+    <t>78970155027721152</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-06 16:15:22</t>
-  </si>
-  <si>
-    <t>2026-07-15 12:04:33</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
+    <t>3235293102 3235293102</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДМ</t>
@@ -490,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -499,15 +505,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -544,154 +552,128 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46209</v>
+        <v>46227</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>61.56</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.49</v>
+        <v>72.48999999999999</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
       </c>
       <c r="H2">
-        <v>91.72</v>
+        <v>1.69</v>
       </c>
       <c r="I2" s="1">
-        <v>1.52</v>
+        <v>122.51</v>
       </c>
       <c r="J2">
-        <v>93.56999999999999</v>
-      </c>
-      <c r="K2" t="s">
+        <v>1.72</v>
+      </c>
+      <c r="K2" s="1">
+        <v>124.68</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <v>185560</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
-        <v>48048</v>
+      <c r="B7" s="7">
+        <v>72.48999999999999</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1.69</v>
+      </c>
+      <c r="E7" s="7">
+        <v>122.51</v>
+      </c>
+      <c r="F7" s="7">
+        <v>124.68</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46218</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3">
-        <v>61.18</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="H3">
-        <v>94.83</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J3">
-        <v>96.66</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3">
-        <v>48563</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="7">
-        <v>122.74</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1.5199</v>
-      </c>
-      <c r="E8" s="7">
-        <v>186.55</v>
-      </c>
-      <c r="F8" s="7">
-        <v>190.23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="10">
-        <v>122.74</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>186.55</v>
-      </c>
-      <c r="F9" s="10">
-        <v>190.23</v>
+    <row r="8" spans="1:14">
+      <c r="A8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="10">
+        <v>72.48999999999999</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
+        <v>122.51</v>
+      </c>
+      <c r="F8" s="10">
+        <v>124.68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -104,7 +104,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="8">
-        <v>1.69</v>
+        <v>1.690026</v>
       </c>
       <c r="E7" s="7">
         <v>122.51</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -496,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,13 +512,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -558,54 +561,60 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46227</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>72.48999999999999</v>
+        <v>72.488</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2">
+        <v>1.619</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.69</v>
       </c>
-      <c r="I2" s="1">
-        <v>122.51</v>
-      </c>
       <c r="J2">
+        <v>122.50472</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.72</v>
       </c>
-      <c r="K2" s="1">
-        <v>124.68</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>124.67936</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2">
         <v>185560</v>
       </c>
-      <c r="N2" t="s">
-        <v>20</v>
+      <c r="O2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -613,59 +622,59 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="7">
-        <v>72.48999999999999</v>
+        <v>72.488</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="8">
-        <v>1.690026</v>
+        <v>1.69</v>
       </c>
       <c r="E7" s="7">
-        <v>122.51</v>
+        <v>122.5</v>
       </c>
       <c r="F7" s="7">
         <v>124.68</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="10">
-        <v>72.48999999999999</v>
+        <v>72.488</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="10">
-        <v>122.51</v>
+        <v>122.5</v>
       </c>
       <c r="F8" s="10">
         <v>124.68</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -105,9 +102,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -201,10 +198,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -512,13 +509,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -561,60 +558,54 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46227</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
       </c>
       <c r="F2">
         <v>72.488</v>
       </c>
       <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2">
+        <v>1.69</v>
+      </c>
+      <c r="I2" s="1">
+        <v>122.505</v>
+      </c>
+      <c r="J2">
+        <v>1.72</v>
+      </c>
+      <c r="K2" s="1">
+        <v>124.679</v>
+      </c>
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="H2">
-        <v>1.619</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J2">
-        <v>122.50472</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L2" s="1">
-        <v>124.67936</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="M2">
+        <v>185560</v>
+      </c>
+      <c r="N2" t="s">
         <v>20</v>
       </c>
-      <c r="N2">
-        <v>185560</v>
-      </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="4" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -622,49 +613,49 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:14">
       <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="7">
         <v>72.488</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <v>1</v>
       </c>
       <c r="D7" s="8">
         <v>1.69</v>
       </c>
-      <c r="E7" s="7">
-        <v>122.5</v>
-      </c>
-      <c r="F7" s="7">
-        <v>124.68</v>
+      <c r="E7" s="8">
+        <v>122.505</v>
+      </c>
+      <c r="F7" s="8">
+        <v>124.679</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="10">
         <v>72.488</v>
@@ -674,10 +665,10 @@
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="10">
-        <v>122.5</v>
+        <v>122.505</v>
       </c>
       <c r="F8" s="10">
-        <v>124.68</v>
+        <v>124.679</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,25 +55,31 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>В4450ТТ</t>
   </si>
   <si>
     <t>В3270ВН</t>
   </si>
   <si>
+    <t>78970155027721160</t>
+  </si>
+  <si>
     <t>78970155027721152</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>16:15:00</t>
-  </si>
-  <si>
-    <t>3235293102 3235293102</t>
+    <t>08:46</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>17:12</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДМ</t>
@@ -102,9 +105,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -198,10 +201,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -505,17 +508,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,125 +557,201 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46239</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46227</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>59.778</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="H2">
+        <v>105.807</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="J2">
+        <v>107.6</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2">
+        <v>49047</v>
+      </c>
+      <c r="M2">
+        <v>289580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46240</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="F2">
-        <v>72.488</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="H2">
-        <v>1.69</v>
-      </c>
-      <c r="I2" s="1">
-        <v>122.505</v>
-      </c>
-      <c r="J2">
-        <v>1.72</v>
-      </c>
-      <c r="K2" s="1">
-        <v>124.679</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
-        <v>185560</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="F3">
+        <v>67.178</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="H3">
+        <v>118.905</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="J3">
+        <v>120.92</v>
+      </c>
+      <c r="K3" t="s">
         <v>20</v>
       </c>
+      <c r="L3">
+        <v>36983</v>
+      </c>
+      <c r="M3">
+        <v>289907</v>
+      </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>50.278</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="H4">
+        <v>88.992</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="J4">
+        <v>90.5</v>
+      </c>
+      <c r="K4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="L4">
+        <v>49447</v>
+      </c>
+      <c r="M4">
+        <v>291748</v>
+      </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="5" t="s">
+    <row r="7" spans="1:13">
+      <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="7">
-        <v>72.488</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1.69</v>
-      </c>
-      <c r="E7" s="8">
-        <v>122.505</v>
-      </c>
-      <c r="F7" s="8">
-        <v>124.679</v>
+    <row r="9" spans="1:13">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="7">
+        <v>177.234</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.77</v>
+      </c>
+      <c r="E9" s="7">
+        <v>313.7</v>
+      </c>
+      <c r="F9" s="7">
+        <v>319.02</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="10">
-        <v>72.488</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10">
-        <v>122.505</v>
-      </c>
-      <c r="F8" s="10">
-        <v>124.679</v>
+    <row r="10" spans="1:13">
+      <c r="A10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="10">
+        <v>177.234</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>313.7</v>
+      </c>
+      <c r="F10" s="10">
+        <v>319.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,31 +58,25 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
-    <t>В4450ТТ</t>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>В3270ВН</t>
   </si>
   <si>
-    <t>78970155027721160</t>
-  </si>
-  <si>
     <t>78970155027721152</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>08:46</t>
-  </si>
-  <si>
-    <t>09:38</t>
-  </si>
-  <si>
-    <t>17:12</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>12:44:00</t>
+  </si>
+  <si>
+    <t>3236622748 3236622748</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДМ</t>
@@ -104,10 +101,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -187,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -201,10 +199,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -508,16 +508,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -557,201 +558,125 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="F2">
-        <v>59.778</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H2">
-        <v>105.807</v>
+      <c r="H2" s="1">
+        <v>1.677</v>
       </c>
       <c r="I2" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J2">
-        <v>107.6</v>
-      </c>
-      <c r="K2" t="s">
+        <v>119.889</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="K2" s="1">
+        <v>130.112</v>
+      </c>
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="L2">
-        <v>49047</v>
-      </c>
       <c r="M2">
-        <v>289580</v>
+        <v>186883</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46240</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="5" spans="1:14">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>67.178</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H3">
-        <v>118.905</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J3">
-        <v>120.92</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>36983</v>
-      </c>
-      <c r="M3">
-        <v>289907</v>
+      <c r="B7" s="7">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1.677</v>
+      </c>
+      <c r="E7" s="7">
+        <v>119.89</v>
+      </c>
+      <c r="F7" s="7">
+        <v>130.11</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46245</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4">
-        <v>50.278</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H4">
-        <v>88.992</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J4">
-        <v>90.5</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4">
-        <v>49447</v>
-      </c>
-      <c r="M4">
-        <v>291748</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="5" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7">
-        <v>177.234</v>
-      </c>
-      <c r="C9" s="7">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.77</v>
-      </c>
-      <c r="E9" s="7">
-        <v>313.7</v>
-      </c>
-      <c r="F9" s="7">
-        <v>319.02</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="10">
-        <v>177.234</v>
-      </c>
-      <c r="C10" s="10">
-        <v>3</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>313.7</v>
-      </c>
-      <c r="F10" s="10">
-        <v>319.02</v>
+      <c r="B8" s="11">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="C8" s="12">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="11">
+        <v>119.89</v>
+      </c>
+      <c r="F8" s="11">
+        <v>130.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДМ/КСУДМ.xlsx
@@ -585,10 +585,10 @@
         <v>18</v>
       </c>
       <c r="H2" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I2" s="1">
-        <v>119.889</v>
+        <v>127.967</v>
       </c>
       <c r="J2" s="1">
         <v>1.82</v>
@@ -647,10 +647,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="9">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="E7" s="7">
-        <v>119.89</v>
+        <v>127.97</v>
       </c>
       <c r="F7" s="7">
         <v>130.11</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="11">
-        <v>119.89</v>
+        <v>127.97</v>
       </c>
       <c r="F8" s="11">
         <v>130.11</v>
